--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,12 +661,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forms Sync Settings</t>
+          <t>Synchronization Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -683,51 +683,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KPTQH26P3CR5WMNQEXQES2C0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTQH26P3CR5WMNQEXQES2C0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Forms Sync Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KPTS9V1WFT919DA7AC3D492E</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTS9V1WFT919DA7AC3D492E</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Form Upload Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,63 +737,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Form Upload Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,98 +913,142 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Forms Sync Settings</t>
+          <t>Candidate Management</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,63 +715,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KPTS9V1WFT919DA7AC3D492E</t>
+          <t>h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTS9V1WFT919DA7AC3D492E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTV18DWNCW5GP7F2TQR9K2B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTV18DW0BVDJTPJJ3STD47Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Forms Sync Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Form Upload Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,63 +781,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Form Upload Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,63 +869,63 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,98 +957,142 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -749,12 +749,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forms Sync Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -771,66 +771,66 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Form Upload Settings</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KNVEEHF11NVNFABDWDV21AEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,85 +979,85 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,32 +1067,10 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">

--- a/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/headings.xlsx
@@ -749,29 +749,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Worker to SFTP</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Candidate to SFTP</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Writeback Map</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,85 +825,85 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Success Execution</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Failure Execution</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,85 +913,85 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Success Execution</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPTV18DWG3VBTF717Q0AMST6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Failure Execution</t>
+          <t>Worker to SFTP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFHC772R0J1BBNZDRRME5H</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Candidate to SFTP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ05GNMHQY0YB35ZWFVGJ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Writeback Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-SFTP-Integration-Setup-Guide/#h_01KPWFJ2RR17RJ9SQH2BZ56061</t>
         </is>
       </c>
     </row>
